--- a/history/volume_history_DPEN_False.xlsx
+++ b/history/volume_history_DPEN_False.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,53 +472,9 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.037410363</v>
+        <v>0.037410444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02754968404769897</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.032250366</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.02754968404769897</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.032204493</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.02754968404769897</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.03237597</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.02754968404769897</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.031762395</v>
-      </c>
-      <c r="C8" t="n">
         <v>0.02754968404769897</v>
       </c>
     </row>
